--- a/audit/aiq-privacy/mcc2026/AIQ_ranked_flight_fee_privacy.xlsx
+++ b/audit/aiq-privacy/mcc2026/AIQ_ranked_flight_fee_privacy.xlsx
@@ -11,7 +11,7 @@
     <sheet name="How this is ranked" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked - flight, fee, privacy'!$A$1:$T$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked - flight, fee, privacy'!$A$1:$Y$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T140"/>
+  <dimension ref="A1:Y140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -506,11 +506,16 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="96" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="46" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -591,25 +596,50 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Nearest airport</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>IATA</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Km airport to campus</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Airport note</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>2025 R1 close</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Academic calendar?</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Evidence URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
@@ -621,7 +651,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ESIC MEDICAL COLLEGE AND HOSPITAL</t>
+          <t>ESIC MEDICAL COLLEGE AND HOSPITAL, INDORE</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -679,11 +709,34 @@
           <t>ESIC central template has no student-list module. Geo-blocked here; user found none from India.</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>INDORE</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Devi Ahilya Bai Holkar</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>In city; LKO direct</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -691,7 +744,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Pt. J N M Medical College</t>
+          <t>Pt. J N M Medical College, Raipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -749,11 +802,34 @@
           <t>813 docs opened, 11 rosters: First_MBBS.pdf (52 rows), MBBS_II_dec2014.pdf (45), UG2017.pdf and U2017.pdf (27 each), plus PG result lists. Newest UG list 2017, nothing after.</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Swami Vivekananda</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>RPR</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>In city; LKO direct</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -761,7 +837,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RG Kar Medical College</t>
+          <t>RG Kar Medical College, Kolkata</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -819,11 +895,34 @@
           <t>/pdf/student-list-jan2012.pdf (53 rows), student-list-jan2010.pdf, student-list-categorywise-2011.pdf. Whole site frozen 2010-2012. Current official site rgkarmch.in is geo-blocked, so this covers only the reachable legacy site.</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Netaji Subhash Chandra Bose</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Shyambazar ~40 min; LKO direct</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -831,7 +930,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Employees State Insurance Corporation Medical College</t>
+          <t>Employees State Insurance Corporation Medical College, Patna</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -889,11 +988,34 @@
           <t>ESIC colleges run on ONE locked central template (*.esic.gov.in) with no student-list module and no per-college admin who could add one. All ESIC sites are geo-blocked from this environment so I could not confirm. User checking from India found no student list, consistent with the template explanation. NMC MSMER portal proforma still needs checking.</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Jay Prakash Narayan</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>PAT</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>In city; LKO direct</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -901,7 +1023,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Employees State Insurance Corporation Medical College</t>
+          <t>Employees State Insurance Corporation Medical College, Kolkata</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -961,25 +1083,48 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Netaji Subhash Chandra Bose</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>Joka, South Kolkata ~1 hr; LKO direct</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>10909</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>https://dhgmc.edu.in</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>dhgmc.edu.in</t>
         </is>
@@ -991,7 +1136,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Burdwan Medical College</t>
+          <t>Burdwan Medical College, Bardhaman (Burdwan</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -1051,25 +1196,48 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>Bardhaman (Burdwan</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Kolkata CCU</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>2.5-3 hr road; LKO direct to Kolkata only</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>11775</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>https://barasatgmch.ac.in</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>barasatgmch.ac.in</t>
         </is>
@@ -1081,7 +1249,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ESIC Medical College and Hospital</t>
+          <t>ESIC Medical College and Hospital, Guwahati</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -1139,11 +1307,34 @@
           <t>ESIC central template has no student-list module. Geo-blocked here; user found none from India.</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Lokpriya Gopinath Bordoloi</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>GAU</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>LKO direct</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1151,7 +1342,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Goa Medical College</t>
+          <t>Goa Medical College, Panaji Goa</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1211,21 +1402,44 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>Panaji Goa</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Dabolim / Mopa</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>GOI / GOX</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>Dabolim ~30 km, Mopa ~35 km; LKO direct</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>12965</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1233,7 +1447,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>College of Medicine and Sagore Dutta Hospital</t>
+          <t>College of Medicine and Sagore Dutta Hospital, Kolkata</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1293,21 +1507,44 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Netaji Subhash Chandra Bose</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>Kamarhati ~40 min; LKO direct</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>8390</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>comsdh.org.in</t>
         </is>
@@ -1319,7 +1556,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>College of Medicine and JNM Hospital</t>
+          <t>College of Medicine and JNM Hospital, Kalyani</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1379,21 +1616,44 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>Kalyani</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Kolkata CCU</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>~1.5 hr road; LKO direct to Kolkata</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>10895</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>comjnmh.ac.in</t>
         </is>
@@ -1405,7 +1665,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College &amp; Hospital</t>
+          <t>Government Medical College &amp; Hospital, Baramati</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1465,11 +1725,34 @@
           <t>Directory literally named brcp/studet_list_mbbs/ holding batch 2020-21, 2021-22, 2022-23, each with a student-name header.</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Baramati</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>PNQ</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>~2.5 hr road; LKO direct to Pune</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1477,7 +1760,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Karur</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1525,11 +1808,34 @@
           <t>Second domain tiruppurmedicalcollege-style: gmchtiruppur/karurgmc pattern. Fee doc found (AIQ_FEES.pdf). Workbook recorded no documents, but a student-merit-list URL exists on the sister domain - treat as unverified.</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Karur</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>TRZ</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>Coimbatore CJB ~130 km alt; no LKO direct</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1537,7 +1843,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Namakkal</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1585,11 +1891,34 @@
           <t>namakkalmedicalcollege.in/page/student-merit-list recorded in evidence column while the summary said no documents. Contradiction in my own data - unverified.</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Namakkal</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>SXV</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>Trichy TRZ ~95 km alt; no LKO direct</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1597,7 +1926,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>North Eastern Indira Gandhi Regional Instt. of Health and Medical Scie</t>
+          <t>North Eastern Indira Gandhi Regional Instt. of Health and Medical Sciences, Shillong</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1647,21 +1976,44 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Guwahati GAU</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>GAU</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>Shillong SHL ~30 km but very limited; LKO direct to Guwahati</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>Puducherry</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>8875</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="2" t="n"/>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1669,7 +2021,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Shaheed Nirmal Mahto Medical College &amp; Hospital</t>
+          <t>Shaheed Nirmal Mahto Medical College &amp; Hospital, Dhanbad</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1717,21 +2069,44 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Durgapur / Ranchi</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>RDP / IXR</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Durgapur ~90 km, Ranchi ~140 km; strong direct rail from LKO</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>9623</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>www.snmmcdhn.org</t>
         </is>
@@ -1789,11 +2164,34 @@
           <t>130 URLs crawled, 0 documents of any kind, no open directories. NOT confirmed against the SPA trap - treat as unverified rather than clean.</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Mandya</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Mysuru / Bengaluru</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>MYQ / BLR</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>Mysuru ~45 km limited, Bengaluru ~130 km; no LKO direct</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1801,7 +2199,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Shyam Shah Medical College</t>
+          <t>Shyam Shah Medical College, Rewa</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1847,11 +2245,34 @@
           <t>110 URLs, 1,611 documents - by far the biggest document surface of any cleared college. Weakest of the clean results.</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Rewa</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Rewa (new) / Prayagraj</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>REW / IXD</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>Rewa airport new and limited; Prayagraj ~230 km</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1859,7 +2280,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Netaji Subhash Chandra Bose Medical College</t>
+          <t>Netaji Subhash Chandra Bose Medical College, Jabalpur</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1905,11 +2326,34 @@
           <t>Angular SPA. No student/document/downloads/academic/calendar endpoint (all 404). /api/notice and /api/results return count 0. News store newest 2020-01-21. Single roster final17.pdf (138 rows, "Name of Student") reachable ONLY by POST to api.nscbmc.ac.in/api/news.</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Dumna</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>JLR</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>~64 flights/wk; NO LKO direct - one stop</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1963,11 +2407,34 @@
           <t>ESIC central template has no student-list module. Geo-blocked here; user found none from India.</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Sahnewal / Chandigarh</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>LUH / IXC</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>Sahnewal very limited; Chandigarh ~100 km, LKO direct</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1975,7 +2442,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ESIC Medical College and Hospital</t>
+          <t>ESIC Medical College and Hospital, VARANASI</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2021,11 +2488,34 @@
           <t>ESIC central template has no student-list module. Geo-blocked here; user found none from India.</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>VARANASI</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Lal Bahadur Shastri</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>VNS</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>In city; ~320 km by road from Lucknow</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2079,11 +2569,34 @@
           <t>Scribd re-host of the 2014 batch.</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Mangaluru / Bengaluru</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>IXE / BLR</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>Both far; no practical day trip</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2091,7 +2604,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Employees State Insurance Corporation Medical College</t>
+          <t>Employees State Insurance Corporation Medical College, Gulbarga</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2139,21 +2652,44 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>Gulbarga</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Kalaburagi / Hyderabad</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>GBI / HYD</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>Kalaburagi limited; Hyderabad ~220 km</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>Karnataka</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>9966</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2161,7 +2697,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Idukki</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -2203,11 +2739,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Idukki</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>COK</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>Madurai IXM ~140 km alt</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2257,11 +2816,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Dharmapuri</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Salem / Hosur</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>SXV</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>Hosur ~90 km alt</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2269,7 +2851,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Pali</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2311,11 +2893,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Pali</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>JDH</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>No LKO direct</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2323,7 +2928,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Pudukkottai</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2365,11 +2970,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Pudukkottai</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>TRZ</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>No LKO direct</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2377,7 +3005,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Bhilwara</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2419,11 +3047,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Bhilwara</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>UDR</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>Jaipur ~250 km alt</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2431,7 +3082,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Bhavnagar</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2473,11 +3124,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>BHU</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>In city; no LKO direct</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2485,7 +3159,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Jammu</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2527,11 +3201,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>IXJ</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>In city</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2539,7 +3236,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh University of Medical Sciences</t>
+          <t>Uttar Pradesh University of Medical Sciences, Etawah</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2581,11 +3278,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Etawah</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Kanpur / Lucknow</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>KNU / LKO</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>Drivable from Lucknow ~230 km - no flight needed</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2593,7 +3313,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Churu</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2635,11 +3355,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Churu</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Jaipur / Bikaner</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>JAI / BKB</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Both far</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2647,7 +3390,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Sher-I-Kashmir Instt. Of Medical Sciences</t>
+          <t>Sher-I-Kashmir Instt. Of Medical Sciences, Srinagar</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2689,11 +3432,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Sheikh ul-Alam</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>In city</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2701,7 +3467,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Nagaur</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2743,11 +3509,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Nagaur</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>JDH</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>No LKO direct</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2755,7 +3544,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Guru Govind Singh Medical College</t>
+          <t>Guru Govind Singh Medical College, Faridkot</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2797,11 +3586,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Faridkot</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Bathinda / Amritsar</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>BUP / ATQ</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>Chandigarh ~200 km alt</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2809,7 +3621,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Bharatpur</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2851,11 +3663,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Bharatpur</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Agra / Delhi</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>AGR / DEL</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>Delhi ~185 km, LKO direct to Delhi</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2863,7 +3698,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Konni</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2905,11 +3740,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Konni</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Trivandrum</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>Cochin ~130 km alt</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2959,11 +3817,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Darbhanga</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Darbhanga</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>DBR</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>In city; Patna ~140 km alt</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2971,7 +3852,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>M G M Medical College</t>
+          <t>M G M Medical College, Jamshedpur</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3013,11 +3894,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Sonari / Ranchi</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>IXW / IXR</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>Sonari very limited; Ranchi ~130 km</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3025,7 +3929,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BPS Government Medical College for Women</t>
+          <t>BPS Government Medical College for Women, Sonepat</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3067,11 +3971,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Sonepat</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>LKO direct to Delhi</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3121,11 +4048,34 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Theni</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>IXM</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>No LKO direct</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3133,7 +4083,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Thiruvallur</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3175,11 +4125,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Thiruvallur</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3187,7 +4150,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Wayanad</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3229,11 +4192,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Wayanad</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="4" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3241,7 +4217,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Dr. Radhakrishnan Government Medical College</t>
+          <t>Dr. Radhakrishnan Government Medical College, Hamirpur</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3283,11 +4259,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Hamirpur</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="4" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="4" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3295,7 +4284,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Nahan</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3337,11 +4326,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Nahan</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="4" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3349,7 +4351,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Alwar</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3391,11 +4393,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Alwar</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="4" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3445,11 +4460,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="4" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3499,11 +4527,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Kasaragod</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="4" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3511,7 +4552,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Rangaraya Medical College</t>
+          <t>Rangaraya Medical College, Kakinada</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3553,11 +4594,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="4" t="inlineStr"/>
-      <c r="T49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3565,7 +4619,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Chittorgarh</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3607,11 +4661,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Chittorgarh</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="4" t="inlineStr"/>
-      <c r="T50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="4" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3619,7 +4686,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Shaikh-UL-Hind Maulana Mahmood Hasan Medical College</t>
+          <t>Shaikh-UL-Hind Maulana Mahmood Hasan Medical College, Saharanpur</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3661,11 +4728,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Saharanpur</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3673,7 +4753,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Haridwar</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3715,11 +4795,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="4" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3769,11 +4862,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Thoothukudi</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R53" s="2" t="inlineStr"/>
-      <c r="S53" s="4" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="4" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr"/>
+      <c r="Y53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3781,7 +4887,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KanyaKumari Government Medical College</t>
+          <t>KanyaKumari Government Medical College, Asaripallam</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3823,11 +4929,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Asaripallam</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="4" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="4" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3835,7 +4954,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Sri Ganganagar</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3877,11 +4996,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Sri Ganganagar</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="4" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="4" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3889,7 +5021,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Barmer</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3931,11 +5063,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Barmer</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3943,7 +5088,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Dr. Bhimrao Ramji Ambedkar</t>
+          <t>Dr. Bhimrao Ramji Ambedkar, Kannauj</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3985,11 +5130,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Kannauj</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="4" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3997,7 +5155,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Sirohi</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -4039,11 +5197,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Sirohi</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4051,7 +5222,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College &amp; Super facility Hospital</t>
+          <t>Government Medical College &amp; Super facility Hospital, Azamgarh</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -4093,11 +5264,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr"/>
-      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Azamgarh</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R59" s="2" t="inlineStr"/>
-      <c r="S59" s="4" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="4" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -4105,7 +5289,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Government Medical College &amp; Hospital (Renamed as Fakir Mohan Medical </t>
+          <t>Government Medical College &amp; Hospital (Renamed as Fakir Mohan Medical College &amp; Hospital), Balasore</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -4147,11 +5331,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Balasore</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R60" s="2" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr"/>
-      <c r="T60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="4" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -4201,11 +5398,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="4" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="4" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -4256,10 +5466,29 @@
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>Devi Ahilya Bai Holkar</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>In city; LKO direct</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr"/>
+      <c r="Y62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -4267,7 +5496,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Vidisha</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -4309,11 +5538,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Vidisha</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R63" s="2" t="inlineStr"/>
-      <c r="S63" s="4" t="inlineStr"/>
-      <c r="T63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="4" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr"/>
+      <c r="Y63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4321,7 +5563,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Tiruppur</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -4363,11 +5605,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R64" s="2" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr"/>
-      <c r="T64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4375,7 +5630,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Kalyan Singh Government Medical College</t>
+          <t>Kalyan Singh Government Medical College, 339</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -4417,11 +5672,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R65" s="2" t="inlineStr"/>
-      <c r="S65" s="4" t="inlineStr"/>
-      <c r="T65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4471,11 +5739,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Thiruvannamalai</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R66" s="2" t="inlineStr"/>
-      <c r="S66" s="4" t="inlineStr"/>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr"/>
+      <c r="Y66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -4483,7 +5764,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Mahamaya Rajkiya Allopathic Medical College</t>
+          <t>Mahamaya Rajkiya Allopathic Medical College, Ambedkarnagar</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -4525,11 +5806,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Ambedkarnagar</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R67" s="2" t="inlineStr"/>
-      <c r="S67" s="4" t="inlineStr"/>
-      <c r="T67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr"/>
+      <c r="Y67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4537,7 +5831,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Government Siddhartha Medical College</t>
+          <t>Government Siddhartha Medical College, Vijaywada</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -4579,11 +5873,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Vijaywada</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="4" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="4" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr"/>
+      <c r="Y68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -4591,7 +5898,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mahraja Jajati Keshari Medical College (previously Government Medical </t>
+          <t>Mahraja Jajati Keshari Medical College (previously Government Medical College and Hospital, Jajpur Odhisha</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -4633,11 +5940,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Jajpur Odhisha</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R69" s="2" t="inlineStr"/>
-      <c r="S69" s="4" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr"/>
+      <c r="Y69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4645,7 +5965,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Shaheed Hasan Khan Mewati Government Medical College</t>
+          <t>Shaheed Hasan Khan Mewati Government Medical College, Nalhar</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -4687,11 +6007,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Nalhar</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr"/>
+      <c r="Y70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4741,11 +6074,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Villupuram</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="4" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4795,11 +6141,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P72" s="2" t="inlineStr"/>
-      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Thiruvarur</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="4" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr"/>
+      <c r="Y72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4807,7 +6166,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Autonomous State Medical College</t>
+          <t>Autonomous State Medical College, Akbarpur</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -4849,11 +6208,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Akbarpur</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="4" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr"/>
+      <c r="Y73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4861,7 +6233,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Dungarpur</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -4903,11 +6275,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Dungarpur</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr"/>
+      <c r="Y74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4915,7 +6300,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Faizabad</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -4957,11 +6342,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
-      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Faizabad</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R75" s="2" t="inlineStr"/>
-      <c r="S75" s="4" t="inlineStr"/>
-      <c r="T75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr"/>
+      <c r="Y75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4969,7 +6367,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Hanumangarh</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -5011,11 +6409,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Hanumangarh</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R76" s="2" t="inlineStr"/>
-      <c r="S76" s="4" t="inlineStr"/>
-      <c r="T76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -5023,7 +6434,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Jaisalmer</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -5065,11 +6476,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
-      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Jaisalmer</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R77" s="2" t="inlineStr"/>
-      <c r="S77" s="4" t="inlineStr"/>
-      <c r="T77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="4" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr"/>
+      <c r="Y77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -5077,7 +6501,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Bundi</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -5119,11 +6543,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Bundi</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R78" s="2" t="inlineStr"/>
-      <c r="S78" s="4" t="inlineStr"/>
-      <c r="T78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr"/>
+      <c r="Y78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -5131,7 +6568,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Rajkiya Medical College Jalaun</t>
+          <t>Rajkiya Medical College Jalaun, Orai</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -5173,11 +6610,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Orai</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R79" s="2" t="inlineStr"/>
-      <c r="S79" s="4" t="inlineStr"/>
-      <c r="T79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr"/>
+      <c r="Y79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -5185,7 +6635,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Dr Vaishampayan Memorial Medical College</t>
+          <t>Dr Vaishampayan Memorial Medical College, Solapur</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -5227,11 +6677,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R80" s="2" t="inlineStr"/>
-      <c r="S80" s="4" t="inlineStr"/>
-      <c r="T80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr"/>
+      <c r="Y80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -5281,11 +6744,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Shimoga</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R81" s="2" t="inlineStr"/>
-      <c r="S81" s="4" t="inlineStr"/>
-      <c r="T81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="4" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr"/>
+      <c r="Y81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -5293,7 +6769,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PT NEKI RAM SHARMA GOVERNMENT MEDICAL COLLEGE</t>
+          <t>PT NEKI RAM SHARMA GOVERNMENT MEDICAL COLLEGE, BHIWANI</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -5335,11 +6811,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr"/>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>BHIWANI</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R82" s="2" t="inlineStr"/>
-      <c r="S82" s="4" t="inlineStr"/>
-      <c r="T82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr"/>
+      <c r="Y82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -5347,7 +6836,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Dholpur</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -5389,11 +6878,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
-      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Dholpur</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr"/>
-      <c r="S83" s="4" t="inlineStr"/>
-      <c r="T83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr"/>
+      <c r="Y83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -5401,7 +6903,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Badaun</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -5443,11 +6945,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Badaun</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R84" s="2" t="inlineStr"/>
-      <c r="S84" s="4" t="inlineStr"/>
-      <c r="T84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr"/>
+      <c r="Y84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -5455,7 +6970,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Rajkiya Allopathic Medical College</t>
+          <t>Rajkiya Allopathic Medical College, Bahraich</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -5497,11 +7012,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr"/>
-      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Bahraich</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R85" s="2" t="inlineStr"/>
-      <c r="S85" s="4" t="inlineStr"/>
-      <c r="T85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="4" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5509,7 +7037,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Dindigul</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -5551,11 +7079,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Dindigul</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R86" s="2" t="inlineStr"/>
-      <c r="S86" s="4" t="inlineStr"/>
-      <c r="T86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="4" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -5563,7 +7104,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Firozabad</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -5605,11 +7146,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
-      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Firozabad</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R87" s="2" t="inlineStr"/>
-      <c r="S87" s="4" t="inlineStr"/>
-      <c r="T87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="4" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr"/>
+      <c r="Y87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5617,7 +7171,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Rajouri</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -5659,11 +7213,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Rajouri</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R88" s="2" t="inlineStr"/>
-      <c r="S88" s="4" t="inlineStr"/>
-      <c r="T88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="4" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr"/>
+      <c r="Y88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -5671,7 +7238,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Government Allopathic Medical College</t>
+          <t>Government Allopathic Medical College, Banda</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -5713,11 +7280,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R89" s="2" t="inlineStr"/>
-      <c r="S89" s="4" t="inlineStr"/>
-      <c r="T89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="4" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr"/>
+      <c r="Y89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5725,7 +7305,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Bettiah</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -5767,11 +7347,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Bettiah</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R90" s="2" t="inlineStr"/>
-      <c r="S90" s="4" t="inlineStr"/>
-      <c r="T90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr"/>
+      <c r="Y90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5779,7 +7372,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Shahjahanpur</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -5821,11 +7414,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr"/>
-      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Shahjahanpur</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R91" s="2" t="inlineStr"/>
-      <c r="S91" s="4" t="inlineStr"/>
-      <c r="T91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="4" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr"/>
+      <c r="Y91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -5833,7 +7439,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Autonomous State Medical College Society</t>
+          <t>Autonomous State Medical College Society, Etah</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -5875,11 +7481,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Etah</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="4" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="4" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr"/>
+      <c r="Y92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -5887,7 +7506,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Banswara</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -5929,11 +7548,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Banswara</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R93" s="2" t="inlineStr"/>
-      <c r="S93" s="4" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="4" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr"/>
+      <c r="Y93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -5984,10 +7616,29 @@
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr"/>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
-      <c r="S94" s="4" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Devi Ahilya Bai Holkar</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>In city; LKO direct</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -5995,7 +7646,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Karauli</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -6037,11 +7688,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Karauli</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="4" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="4" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr"/>
+      <c r="Y95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -6049,7 +7713,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Dr. Shankarrao Chavan Govt. Medical College</t>
+          <t>Dr. Shankarrao Chavan Govt. Medical College, Nanded</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -6091,11 +7755,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="4" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="4" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr"/>
+      <c r="Y96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -6103,7 +7780,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Government medical college</t>
+          <t>Government medical college, tonk</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -6145,11 +7822,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr"/>
-      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>tonk</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R97" s="2" t="inlineStr"/>
-      <c r="S97" s="4" t="inlineStr"/>
-      <c r="T97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="4" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr"/>
+      <c r="Y97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6157,7 +7847,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Late Shri Baliram Kashyap Memorial NDMC Govt. Medical College</t>
+          <t>Late Shri Baliram Kashyap Memorial NDMC Govt. Medical College, Jagdalpur</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -6199,11 +7889,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Jagdalpur</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="4" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="4" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr"/>
+      <c r="Y98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -6211,7 +7914,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Rampur</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -6253,11 +7956,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Rampur</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R99" s="2" t="inlineStr"/>
-      <c r="S99" s="4" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="4" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr"/>
+      <c r="Y99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6265,7 +7981,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Baran</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6307,11 +8023,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr"/>
-      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>Baran</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="4" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="4" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr"/>
+      <c r="Y100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -6319,7 +8048,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College Janjgir</t>
+          <t>Government Medical College Janjgir, Champa</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -6361,11 +8090,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr"/>
-      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Champa</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="4" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="4" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr"/>
+      <c r="Y101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6373,7 +8115,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Kathua</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
@@ -6415,11 +8157,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr"/>
-      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Kathua</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="4" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="4" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr"/>
+      <c r="Y102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -6427,7 +8182,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Autonomous State Medical College Society</t>
+          <t>Autonomous State Medical College Society, Fatehpur</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
@@ -6469,11 +8224,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr"/>
-      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Fatehpur</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R103" s="2" t="inlineStr"/>
-      <c r="S103" s="4" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="4" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr"/>
+      <c r="Y103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6481,7 +8249,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Dharanidhar Medical College and Hospital (previously Government Medica</t>
+          <t>Dharanidhar Medical College and Hospital (previously Government Medical College, Keonjhar</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
@@ -6523,11 +8291,24 @@
           <t>Not audited - site unreachable from this environment, or never in the worklist</t>
         </is>
       </c>
-      <c r="P104" s="2" t="inlineStr"/>
-      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Keonjhar</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="4" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="4" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr"/>
+      <c r="Y104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -6535,7 +8316,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Sri Jagannath Medical College &amp; Hospital</t>
+          <t>Sri Jagannath Medical College &amp; Hospital, Puri</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
@@ -6579,21 +8360,44 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
+          <t>Puri</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>Salem / Hosur</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>SXV</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="T105" s="4" t="inlineStr">
+        <is>
+          <t>Hosur ~90 km alt</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="Q105" s="2" t="inlineStr">
+      <c r="V105" s="2" t="inlineStr">
         <is>
           <t>8718</t>
         </is>
       </c>
-      <c r="R105" s="2" t="inlineStr">
+      <c r="W105" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S105" s="4" t="n"/>
-      <c r="T105" s="2" t="inlineStr">
+      <c r="X105" s="2" t="n"/>
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>sjmch.odisha.gov.in</t>
         </is>
@@ -6605,7 +8409,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Indira Gandhi Medical College &amp; Research Institute</t>
+          <t>Indira Gandhi Medical College &amp; Research Institute, Puducherry</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
@@ -6654,16 +8458,29 @@
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="4" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
           <t>8875</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S106" s="4" t="n"/>
-      <c r="T106" s="2" t="n"/>
+      <c r="X106" s="2" t="n"/>
+      <c r="Y106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -6671,7 +8488,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>VARDHMAN INSTITUTE OF MEDICAL SCIENCES</t>
+          <t>VARDHMAN INSTITUTE OF MEDICAL SCIENCES, NALANDA</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
@@ -6717,11 +8534,24 @@
           <t>nmchpatna.ac.in publishes 18 sessions of student lists, 2006-07 through 2024-25. This was the audit brief exemplar used to validate the detector.</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr"/>
-      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>NALANDA</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R107" s="2" t="inlineStr"/>
-      <c r="S107" s="4" t="inlineStr"/>
-      <c r="T107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="4" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr"/>
+      <c r="Y107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6729,7 +8559,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Shri Atal Bihari Vajpayee Government Medical College</t>
+          <t>Shri Atal Bihari Vajpayee Government Medical College, Faridabad</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -6773,25 +8603,38 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="4" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="Q108" s="2" t="inlineStr">
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>8827</t>
         </is>
       </c>
-      <c r="R108" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S108" s="4" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>https://abvgmcvidisha.edu.in/msrinfo.html</t>
         </is>
       </c>
-      <c r="T108" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>abvgmcvidisha.edu.in</t>
         </is>
@@ -6803,7 +8646,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Pt. Jawahar Lal Nehru Government Medical College</t>
+          <t>Pt. Jawahar Lal Nehru Government Medical College, Chamba</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -6847,25 +8690,38 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
+          <t>Chamba</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="4" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="V109" s="2" t="inlineStr">
         <is>
           <t>8222</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="W109" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S109" s="4" t="inlineStr">
+      <c r="X109" s="2" t="inlineStr">
         <is>
           <t>https://gmcchamba.edu.in/student-corner-2/</t>
         </is>
       </c>
-      <c r="T109" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>gmcchamba.edu.in</t>
         </is>
@@ -6877,7 +8733,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>NAMO Medical Education &amp; Research Institute</t>
+          <t>NAMO Medical Education &amp; Research Institute, Silvassa</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
@@ -6925,25 +8781,38 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="4" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
           <t>DNH &amp; DD</t>
         </is>
       </c>
-      <c r="Q110" s="2" t="inlineStr">
+      <c r="V110" s="2" t="inlineStr">
         <is>
           <t>8069</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
+      <c r="W110" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S110" s="4" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>https://namomeridnhdd.in/admitted-student-in-ug-details</t>
         </is>
       </c>
-      <c r="T110" s="2" t="inlineStr">
+      <c r="Y110" s="2" t="inlineStr">
         <is>
           <t>namomeridnhdd.in</t>
         </is>
@@ -6955,7 +8824,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Kakatiya Medical College</t>
+          <t>Kakatiya Medical College, Warangal</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -7003,25 +8872,38 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="4" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="Q111" s="2" t="inlineStr">
+      <c r="V111" s="2" t="inlineStr">
         <is>
           <t>8974</t>
         </is>
       </c>
-      <c r="R111" s="2" t="inlineStr">
+      <c r="W111" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S111" s="4" t="inlineStr">
+      <c r="X111" s="2" t="inlineStr">
         <is>
           <t>https://www.kmcwgl.com/ug-year-wise-list---25-26.html</t>
         </is>
       </c>
-      <c r="T111" s="2" t="inlineStr">
+      <c r="Y111" s="2" t="inlineStr">
         <is>
           <t>www.kmcwgl.com</t>
         </is>
@@ -7033,7 +8915,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>S V Medical College</t>
+          <t>S V Medical College, Tirupati</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -7079,11 +8961,24 @@
           <t>1,776 docs, 7 roster hits including a 2025-26 PG prospectus; B.1.11 page links UG name lists, 240 rows against 240 sanctioned seats.</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R112" s="2" t="inlineStr"/>
-      <c r="S112" s="4" t="inlineStr"/>
-      <c r="T112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="4" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr"/>
+      <c r="Y112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -7091,7 +8986,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College &amp; Hospital (Renamed as Bhima Bhoi Medical C</t>
+          <t>Government Medical College &amp; Hospital (Renamed as Bhima Bhoi Medical College &amp; Hospital), Balangir</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -7135,21 +9030,34 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
+          <t>Balangir</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="4" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="Q113" s="2" t="inlineStr">
+      <c r="V113" s="2" t="inlineStr">
         <is>
           <t>12424</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="W113" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S113" s="4" t="n"/>
-      <c r="T113" s="2" t="n"/>
+      <c r="X113" s="2" t="n"/>
+      <c r="Y113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -7157,7 +9065,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Sawai Madhopur</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
@@ -7201,21 +9109,34 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
+          <t>Sawai Madhopur</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="4" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="Q114" s="2" t="inlineStr">
+      <c r="V114" s="2" t="inlineStr">
         <is>
           <t>11726</t>
         </is>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="W114" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S114" s="4" t="n"/>
-      <c r="T114" s="2" t="n"/>
+      <c r="X114" s="2" t="n"/>
+      <c r="Y114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -7223,7 +9144,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Shri Krishna Medical College</t>
+          <t>Shri Krishna Medical College, Muzzafarpur</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
@@ -7267,21 +9188,34 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
+          <t>Muzzafarpur</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="4" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="Q115" s="2" t="inlineStr">
+      <c r="V115" s="2" t="inlineStr">
         <is>
           <t>10119</t>
         </is>
       </c>
-      <c r="R115" s="2" t="inlineStr">
+      <c r="W115" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S115" s="4" t="n"/>
-      <c r="T115" s="2" t="inlineStr">
+      <c r="X115" s="2" t="n"/>
+      <c r="Y115" s="2" t="inlineStr">
         <is>
           <t>skmedicalcollege.org</t>
         </is>
@@ -7293,7 +9227,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Dausa</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
@@ -7337,21 +9271,34 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
+          <t>Dausa</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="4" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="Q116" s="2" t="inlineStr">
+      <c r="V116" s="2" t="inlineStr">
         <is>
           <t>9156</t>
         </is>
       </c>
-      <c r="R116" s="2" t="inlineStr">
+      <c r="W116" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S116" s="4" t="n"/>
-      <c r="T116" s="2" t="n"/>
+      <c r="X116" s="2" t="n"/>
+      <c r="Y116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7359,7 +9306,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Jhunjhunu</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
@@ -7405,11 +9352,24 @@
           <t>Scribd re-host: MBBS batch 2024-25, 100 students, names + fathers names.</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr"/>
-      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Jhunjhunu</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R117" s="2" t="inlineStr"/>
-      <c r="S117" s="4" t="inlineStr"/>
-      <c r="T117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="4" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr"/>
+      <c r="Y117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -7417,7 +9377,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Bundelkhand Medical College</t>
+          <t>Bundelkhand Medical College, Sagar</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
@@ -7461,21 +9421,34 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="4" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="Q118" s="2" t="inlineStr">
+      <c r="V118" s="2" t="inlineStr">
         <is>
           <t>9704</t>
         </is>
       </c>
-      <c r="R118" s="2" t="inlineStr">
+      <c r="W118" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S118" s="4" t="n"/>
-      <c r="T118" s="2" t="inlineStr">
+      <c r="X118" s="2" t="n"/>
+      <c r="Y118" s="2" t="inlineStr">
         <is>
           <t>bmcsagar.edu.in</t>
         </is>
@@ -7487,7 +9460,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru Medical College</t>
+          <t>Jawaharlal Nehru Medical College, Bhagalpur</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
@@ -7531,25 +9504,38 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
+          <t>Bhagalpur</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="4" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="Q119" s="2" t="inlineStr">
+      <c r="V119" s="2" t="inlineStr">
         <is>
           <t>8746</t>
         </is>
       </c>
-      <c r="R119" s="2" t="inlineStr">
+      <c r="W119" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S119" s="4" t="inlineStr">
+      <c r="X119" s="2" t="inlineStr">
         <is>
           <t>https://jlnmcbgp.org/student-corner</t>
         </is>
       </c>
-      <c r="T119" s="2" t="inlineStr">
+      <c r="Y119" s="2" t="inlineStr">
         <is>
           <t>jlnmcbgp.org</t>
         </is>
@@ -7561,7 +9547,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Anugrah Narayan Magadh Medical College</t>
+          <t>Anugrah Narayan Magadh Medical College, Gaya</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
@@ -7605,21 +9591,34 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="4" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="Q120" s="2" t="inlineStr">
+      <c r="V120" s="2" t="inlineStr">
         <is>
           <t>10932</t>
         </is>
       </c>
-      <c r="R120" s="2" t="inlineStr">
+      <c r="W120" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S120" s="4" t="n"/>
-      <c r="T120" s="2" t="inlineStr">
+      <c r="X120" s="2" t="n"/>
+      <c r="Y120" s="2" t="inlineStr">
         <is>
           <t>anmmc.ac.in</t>
         </is>
@@ -7631,7 +9630,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Dr. LAXMINARAYAN PANDEY GOVT. MEDICAL COLLEGE</t>
+          <t>Dr. LAXMINARAYAN PANDEY GOVT. MEDICAL COLLEGE, RATLAM</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
@@ -7675,25 +9674,38 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
+          <t>RATLAM</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="4" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="Q121" s="2" t="inlineStr">
+      <c r="V121" s="2" t="inlineStr">
         <is>
           <t>10378</t>
         </is>
       </c>
-      <c r="R121" s="2" t="inlineStr">
+      <c r="W121" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S121" s="4" t="inlineStr">
+      <c r="X121" s="2" t="inlineStr">
         <is>
           <t>https://gmcratlam.org/student-section.aspx</t>
         </is>
       </c>
-      <c r="T121" s="2" t="inlineStr">
+      <c r="Y121" s="2" t="inlineStr">
         <is>
           <t>gmcratlam.org</t>
         </is>
@@ -7705,7 +9717,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Veer Chandra Singh Garhwali Govt. Medical Sc. &amp; Research Instt</t>
+          <t>Veer Chandra Singh Garhwali Govt. Medical Sc. &amp; Research Instt, Pauri Garhwal</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -7749,25 +9761,38 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
+          <t>Pauri Garhwal</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="4" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="Q122" s="2" t="inlineStr">
+      <c r="V122" s="2" t="inlineStr">
         <is>
           <t>9965</t>
         </is>
       </c>
-      <c r="R122" s="2" t="inlineStr">
+      <c r="W122" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S122" s="4" t="inlineStr">
+      <c r="X122" s="2" t="inlineStr">
         <is>
           <t>https://vcsgsrinagar.org</t>
         </is>
       </c>
-      <c r="T122" s="2" t="inlineStr">
+      <c r="Y122" s="2" t="inlineStr">
         <is>
           <t>vcsgsrinagar.org</t>
         </is>
@@ -7779,7 +9804,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Pt. Raghunath Murmu Medical College and Hospital</t>
+          <t>Pt. Raghunath Murmu Medical College and Hospital, Baripada</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
@@ -7823,21 +9848,34 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
+          <t>Baripada</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="4" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="Q123" s="2" t="inlineStr">
+      <c r="V123" s="2" t="inlineStr">
         <is>
           <t>12463</t>
         </is>
       </c>
-      <c r="R123" s="2" t="inlineStr">
+      <c r="W123" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S123" s="4" t="n"/>
-      <c r="T123" s="2" t="n"/>
+      <c r="X123" s="2" t="n"/>
+      <c r="Y123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7845,7 +9883,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, The Nilgiris</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
@@ -7891,11 +9929,24 @@
           <t>/page/list-of-student serves per-batch name PDFs including batch-2025-26-list-of-students.pdf (header NAME, serials to 150).</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr"/>
-      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>The Nilgiris</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R124" s="2" t="inlineStr"/>
-      <c r="S124" s="4" t="inlineStr"/>
-      <c r="T124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="4" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr"/>
+      <c r="Y124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -7903,7 +9954,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Soban Singh jeena Government institute of Medical science &amp; Research</t>
+          <t>Soban Singh jeena Government institute of Medical science &amp; Research, Almora</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -7947,21 +9998,34 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
+          <t>Almora</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="4" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="Q125" s="2" t="inlineStr">
+      <c r="V125" s="2" t="inlineStr">
         <is>
           <t>11917</t>
         </is>
       </c>
-      <c r="R125" s="2" t="inlineStr">
+      <c r="W125" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S125" s="4" t="n"/>
-      <c r="T125" s="2" t="inlineStr">
+      <c r="X125" s="2" t="n"/>
+      <c r="Y125" s="2" t="inlineStr">
         <is>
           <t>www.ssjgimsralmora.org</t>
         </is>
@@ -8017,21 +10081,34 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
+          <t>cuddalore</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="4" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="inlineStr">
+      <c r="V126" s="2" t="inlineStr">
         <is>
           <t>9926</t>
         </is>
       </c>
-      <c r="R126" s="2" t="inlineStr">
+      <c r="W126" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S126" s="4" t="n"/>
-      <c r="T126" s="2" t="n"/>
+      <c r="X126" s="2" t="n"/>
+      <c r="Y126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -8039,7 +10116,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Vijaynagar Institute of Medical Sciences</t>
+          <t>Vijaynagar Institute of Medical Sciences, Bellary</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
@@ -8083,21 +10160,34 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
+          <t>Bellary</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="4" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
           <t>Karnataka</t>
         </is>
       </c>
-      <c r="Q127" s="2" t="inlineStr">
+      <c r="V127" s="2" t="inlineStr">
         <is>
           <t>11026</t>
         </is>
       </c>
-      <c r="R127" s="2" t="inlineStr">
+      <c r="W127" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S127" s="4" t="n"/>
-      <c r="T127" s="2" t="n"/>
+      <c r="X127" s="2" t="n"/>
+      <c r="Y127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -8105,7 +10195,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Shivpuri</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
@@ -8153,21 +10243,34 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
+          <t>Shivpuri</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="4" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="Q128" s="2" t="inlineStr">
+      <c r="V128" s="2" t="inlineStr">
         <is>
           <t>11464</t>
         </is>
       </c>
-      <c r="R128" s="2" t="inlineStr">
+      <c r="W128" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S128" s="4" t="n"/>
-      <c r="T128" s="2" t="inlineStr">
+      <c r="X128" s="2" t="n"/>
+      <c r="Y128" s="2" t="inlineStr">
         <is>
           <t>shivpurimedicalcollege.com</t>
         </is>
@@ -8179,7 +10282,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>North Bengal Medical College</t>
+          <t>North Bengal Medical College, Darjeeling</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
@@ -8223,21 +10326,34 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
+          <t>Darjeeling</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="4" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q129" s="2" t="inlineStr">
+      <c r="V129" s="2" t="inlineStr">
         <is>
           <t>10533</t>
         </is>
       </c>
-      <c r="R129" s="2" t="inlineStr">
+      <c r="W129" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S129" s="4" t="n"/>
-      <c r="T129" s="2" t="inlineStr">
+      <c r="X129" s="2" t="n"/>
+      <c r="Y129" s="2" t="inlineStr">
         <is>
           <t>nbmch.ac.in</t>
         </is>
@@ -8249,7 +10365,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Virendra Kumar Sakhlecha Government Medical College</t>
+          <t>Virendra Kumar Sakhlecha Government Medical College, Kanawati</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -8293,21 +10409,34 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
+          <t>Kanawati</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="4" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="Q130" s="2" t="inlineStr">
+      <c r="V130" s="2" t="inlineStr">
         <is>
           <t>12370</t>
         </is>
       </c>
-      <c r="R130" s="2" t="inlineStr">
+      <c r="W130" s="2" t="inlineStr">
         <is>
           <t>site not reachable</t>
         </is>
       </c>
-      <c r="S130" s="4" t="n"/>
-      <c r="T130" s="2" t="n"/>
+      <c r="X130" s="2" t="n"/>
+      <c r="Y130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -8315,7 +10444,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Diamond Harbour Government Medical College and Hospital</t>
+          <t>Diamond Harbour Government Medical College and Hospital, West Bengal</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -8364,20 +10493,33 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="4" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
           <t>10909</t>
         </is>
       </c>
-      <c r="R131" s="2" t="inlineStr">
+      <c r="W131" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S131" s="4" t="inlineStr">
+      <c r="X131" s="2" t="inlineStr">
         <is>
           <t>https://dhgmc.edu.in</t>
         </is>
       </c>
-      <c r="T131" s="2" t="inlineStr">
+      <c r="Y131" s="2" t="inlineStr">
         <is>
           <t>dhgmc.edu.in</t>
         </is>
@@ -8389,7 +10531,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Assam Medial College</t>
+          <t>Assam Medial College, Dibrugarh</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -8433,21 +10575,34 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="4" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="Q132" s="2" t="inlineStr">
+      <c r="V132" s="2" t="inlineStr">
         <is>
           <t>11571</t>
         </is>
       </c>
-      <c r="R132" s="2" t="inlineStr">
+      <c r="W132" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S132" s="4" t="n"/>
-      <c r="T132" s="2" t="inlineStr">
+      <c r="X132" s="2" t="n"/>
+      <c r="Y132" s="2" t="inlineStr">
         <is>
           <t>amch-dibrugarh.assam.gov.in</t>
         </is>
@@ -8503,25 +10658,38 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
+          <t>Bankura</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="4" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="Q133" s="2" t="inlineStr">
+      <c r="V133" s="2" t="inlineStr">
         <is>
           <t>11895</t>
         </is>
       </c>
-      <c r="R133" s="2" t="inlineStr">
+      <c r="W133" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S133" s="4" t="inlineStr">
+      <c r="X133" s="2" t="inlineStr">
         <is>
           <t>https://bsmedicalcollege.org.in/pdf/UG-New-istyr.pdf</t>
         </is>
       </c>
-      <c r="T133" s="2" t="inlineStr">
+      <c r="Y133" s="2" t="inlineStr">
         <is>
           <t>bsmedicalcollege.org.in</t>
         </is>
@@ -8533,7 +10701,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Datia</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -8579,11 +10747,24 @@
           <t>B.1.11 disclosure page, batch2025, 136 rows.</t>
         </is>
       </c>
-      <c r="P134" s="2" t="inlineStr"/>
-      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>Datia</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R134" s="2" t="inlineStr"/>
-      <c r="S134" s="4" t="inlineStr"/>
-      <c r="T134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="4" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr"/>
+      <c r="Y134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -8591,7 +10772,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Saheed Laxman Nayak Medical College &amp; Hospital</t>
+          <t>Saheed Laxman Nayak Medical College &amp; Hospital, Koraput</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -8635,21 +10816,34 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
+          <t>Koraput</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="4" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="Q135" s="2" t="inlineStr">
+      <c r="V135" s="2" t="inlineStr">
         <is>
           <t>9193</t>
         </is>
       </c>
-      <c r="R135" s="2" t="inlineStr">
+      <c r="W135" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S135" s="4" t="n"/>
-      <c r="T135" s="2" t="inlineStr">
+      <c r="X135" s="2" t="n"/>
+      <c r="Y135" s="2" t="inlineStr">
         <is>
           <t>slnmch.nic.in</t>
         </is>
@@ -8661,7 +10855,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Chhattisgarh Institute of Medical Sciences</t>
+          <t>Chhattisgarh Institute of Medical Sciences, Bilaspur</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -8709,11 +10903,24 @@
           <t>755 documents opened, ZERO roster hits. More docs opened than any other cleared college (Ambajogai 388, Chandrapur 186). Publishes an academic calendar.</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr"/>
-      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R136" s="2" t="inlineStr"/>
-      <c r="S136" s="4" t="inlineStr"/>
-      <c r="T136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="4" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr"/>
+      <c r="Y136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -8721,7 +10928,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Miraj</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -8769,11 +10976,24 @@
           <t>Scanned-image UG admission PDF with no extractable text - PROVISIONAL pending OCR, never cleared.</t>
         </is>
       </c>
-      <c r="P137" s="2" t="inlineStr"/>
-      <c r="Q137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Miraj</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R137" s="2" t="inlineStr"/>
-      <c r="S137" s="4" t="inlineStr"/>
-      <c r="T137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="4" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr"/>
+      <c r="Y137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -8781,7 +11001,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Government Medical College</t>
+          <t>Government Medical College, Nashik</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -8829,11 +11049,24 @@
           <t>MBBS Student List Batch 2025.pdf (Final Retention Data 2025-26) and Batch 2024.pdf from its NMC Information page.</t>
         </is>
       </c>
-      <c r="P138" s="2" t="inlineStr"/>
-      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
       <c r="R138" s="2" t="inlineStr"/>
-      <c r="S138" s="4" t="inlineStr"/>
-      <c r="T138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr"/>
+      <c r="T138" s="4" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr"/>
+      <c r="Y138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -8841,7 +11074,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi Institute of Medical Sciences</t>
+          <t>Mahatma Gandhi Institute of Medical Sciences, Sevagram</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -8887,25 +11120,38 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
+          <t>Sevagram</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="4" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="Q139" s="2" t="inlineStr">
+      <c r="V139" s="2" t="inlineStr">
         <is>
           <t>9917</t>
         </is>
       </c>
-      <c r="R139" s="2" t="inlineStr">
+      <c r="W139" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S139" s="4" t="inlineStr">
+      <c r="X139" s="2" t="inlineStr">
         <is>
           <t>https://mgims.ac.in/index.php/about-us/mci-requirements</t>
         </is>
       </c>
-      <c r="T139" s="2" t="inlineStr">
+      <c r="Y139" s="2" t="inlineStr">
         <is>
           <t>mgims.ac.in</t>
         </is>
@@ -8917,7 +11163,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Rajashree Chatrapati Shahu Maharaj Government Medical College</t>
+          <t>Rajashree Chatrapati Shahu Maharaj Government Medical College, Kolhapur</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -8963,32 +11209,45 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>not resolved</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="4" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="Q140" s="2" t="inlineStr">
+      <c r="V140" s="2" t="inlineStr">
         <is>
           <t>11177</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
+      <c r="W140" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S140" s="4" t="inlineStr">
+      <c r="X140" s="2" t="inlineStr">
         <is>
           <t>https://rcsmgmc.ac.in</t>
         </is>
       </c>
-      <c r="T140" s="2" t="inlineStr">
+      <c r="Y140" s="2" t="inlineStr">
         <is>
           <t>rcsmgmc.ac.in</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T140"/>
+  <autoFilter ref="A1:Y140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
